--- a/output/第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx
+++ b/output/第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>指数による概算では、令和11年度の月額基準額は案A 6,684円・案B 6,593円・案C 6,789円です。第1段階から第3段階まで通して再計算した案Cは6,755円です。</t>
+          <t>指数による概算では、令和11年度の月額基準額は案A 6,684円・案B 6,593円・案C 6,789円です。第1段階から第3段階まで通して再計算した案Cは6,740円です。</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>6,684円</t>
+          <t>6,670円</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>6,593円</t>
+          <t>6,578円</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>6,789円</t>
+          <t>6,774円</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>6,789円</t>
+          <t>6,774円</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>+389円</t>
+          <t>+374円</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr"/>
@@ -3068,12 +3068,12 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>6,755円</t>
+          <t>6,740円</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>+355円</t>
+          <t>+340円</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>A 社人研、B 社人研＋補正、C 総合戦略・住民基本台帳の実績趨勢。概算による令和11年度の月額基準額は6,684円・6,593円・6,789円、通し再計算による案Cは6,755円です。</t>
+          <t>A 社人研、B 社人研＋補正、C 総合戦略・住民基本台帳の実績趨勢。概算による令和11年度の月額基準額は6,684円・6,593円・6,789円、通し再計算による案Cは6,740円です。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">

--- a/output/第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx
+++ b/output/第10期計画_人口推計の基礎の変更_総合戦略ベース.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>指数による概算では、令和11年度の月額基準額は案A 6,684円・案B 6,593円・案C 6,789円です。第1段階から第3段階まで通して再計算した案Cは6,740円です。</t>
+          <t>指数による概算では、令和11年度の月額基準額は案A 6,670円・案B 6,578円・案C 6,774円です。第1段階から第3段階まで通して再計算した案Cは6,740円です。</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2635,7 +2635,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>社人研を基礎としていたときの月額6,684円を基準として、人口の基礎を変えた場合の影響を示します。【1】〜【3】は給付費が認定者数に比例すると仮定した概算、【4】は通して再計算した結果です。</t>
+          <t>社人研を基礎としていたときの月額6,670円を基準として、人口の基礎を変えた場合の影響を示します。【1】〜【3】は給付費が認定者数に比例すると仮定した概算、【4】は通して再計算した結果です。</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>6,684円</t>
+          <t>6,670円</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>+284円</t>
+          <t>+270円</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr"/>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>A 社人研、B 社人研＋補正、C 総合戦略・住民基本台帳の実績趨勢。概算による令和11年度の月額基準額は6,684円・6,593円・6,789円、通し再計算による案Cは6,740円です。</t>
+          <t>A 社人研、B 社人研＋補正、C 総合戦略・住民基本台帳の実績趨勢。概算による令和11年度の月額基準額は6,670円・6,578円・6,774円、通し再計算による案Cは6,740円です。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
